--- a/output/第10期計画_内部確認結果への対応整理.xlsx
+++ b/output/第10期計画_内部確認結果への対応整理.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_構成3町への確認事項" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_8月26日打合せ顛末との突合" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_新たに生じた確認事項" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_KPIの優先順位（追加資料なしの前提）" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -124,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -159,6 +160,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -841,6 +845,1402 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>代表KPIの優先順位（追加提供資料が見込めない前提）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="56" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>内部確認結果2項の「『評価困難』『指標不足』とされている事項について、広域連合のみで追加して提供できる資料は現時点では多くない」とのご回答を前提に、16項目を5つの観点で採点し優先順位を付けたものです。受領済み・公表資料だけで算定できるかを第一の基準としています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>順</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>データ源</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>①追加
+提供</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>②保険料
+算定</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>③更新
+頻度</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>④事務
+負担</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>⑤比較
+可能性</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>追加提供がない場合の扱い</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>H01</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>年齢調整済要介護認定率（性・年齢調整済み要介護2以上）</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>見える化W144（交付金評価指標Ⅳ-5）</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>本文の成果指標。基準値9.25％（R5調査）は確定済みで、毎年度、国が全保険者を共通の方法で算定する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>H02</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>要介護3以上認定率</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>見える化B4-a</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>本文の成果指標。基準値6.3％（R8年3月末）は確定済み。粗率のため他団体比較は年齢構成の影響を受ける。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>H15</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>給付費の計画乖離率</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>介護保険特別会計決算／見える化</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>本文の成果指標。R6 ▲3.66％・R7 ▲2.17％は確定済み。決算は毎年度受領する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>H13</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>職種別従事者数の推移（認定者1万対）</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>見える化M2-a〜m</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>本文の成果指標。基準値535.17（介護老人福祉施設・R6）は確定済み。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>H05</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>月1回以上の社会参加率</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>総合事業実施状況調査（通いの場）</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>本文の成果指標。データ源を総合事業実施状況調査に一本化すれば毎年度算定できる（R6 3.53％）。健康とくらしの調査による6区分合成36.0％は3年に1度である。どの値を基準とするかの決定を要する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="64" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>H04</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>フレイル該当割合</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>健康とくらしの調査（基本チェックリスト）</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>本文の成果指標。基準値19.1％は確定済みだが3年に1度である。目標は第11期策定時の調査で確認する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>H03</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>75歳以上新規認定率</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>介護リームス（新規認定者数）</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>本文の成果指標。広域連合が保有するシステムからの1回の抽出で確保できる。外部への追加依頼ではない。抽出が得られない場合は優先度Dとなる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>H16</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>業務継続計画を策定している事業所の割合</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>国民健康保険団体連合会の給付実績（業務継続計画未策定減算）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>受領済みの給付費データに減算の算定状況が含まれるかを確認する。含まれていれば毎年度算定でき本文の成果指標とする。含まれない場合は国保連の給付実績の抽出を要するため、指標から外す。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>H12</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>区域内で提供できないサービスが必要と判断された利用者の割合</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>在宅生活改善調査 問3</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>資料編に基準値のみ（20.4％・98票中20票）。24時間対応サービスの整備の判断材料として重要だが3年に1度でしか更新されない。年次評価には、区域内に事業所がないサービスの数（毎年度、北海道の指定事業所一覧で確認できる）を用いる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>H07</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>主に介護をしている者の割合</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>健康とくらしの調査 サブコア1【問17】4）</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>資料編に基準値のみ（3.4％・n=2,217）。指標の定義変更の決定を要する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="64" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>H11</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>供給不足を理由とする住替え割合（補完）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>健康とくらしの調査【大雪－問3】1）2）</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="K15" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>資料編に基準値のみ（補完値5.4％・n=4,446）。居所変更実態調査は把握率58.1％のため基準値としにくい。供給不足の把握は待機者数と区域外利用率（見える化）で代替する。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>H06</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>在宅生活継続困難割合</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>健康とくらしの調査【大雪－問2】1）2）</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>資料編に基準値のみ（補完値0.6％・n=4,128）。大雪独自設問のため他団体と比較できない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="64" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>H08</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>世話をしてくれる人がいない者の割合（補完）</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>健康とくらしの調査【大雪－問4】1）</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>資料編に基準値のみ（8.7％・n=4,599）。H07と領域が重なる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="64" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>H14</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>採用率と離職率の差（補完）</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>介護人材実態調査</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>指標から外す。各年9月30日現在の在籍者数を事業所に新たに求めることになる。代替は下表のとおり。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="64" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>H09</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>退院時支援調整実施率</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>3町の地域包括支援センターの業務記録</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>指標から外し、施策のアウトプットに置き換える。新たな記録様式の整備を3町の包括に求めることになる。代替は下表のとおり。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="64" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>H10</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>認知症相談から支援接続までの適時率</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>指標から外し、施策のアウトプットに置き換える。代替は下表のとおり。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>観点</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>3点</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>2点</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>1点</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>0点</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr"/>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr"/>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>①追加提供の要否</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>既受領・公表資料のみで算定済み</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>既受領資料で算定できるが指標の定義変更の決定を要する</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>広域連合内のシステム等から1回の抽出を要する</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>新たな調査・記録様式・事業所への照会を要する</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>②保険料算定・介護保険運営との関係</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>直結（認定率・給付費・見込量・保険料）</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>見込量又は施策の根拠</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>③更新の頻度</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>毎年度</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>3年に1度だが毎年度の代替値がある</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>3年に1度</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>更新の見込みがない</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>④構成町・事業所の事務負担</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>小（既存の実績報告の範囲）</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>大（新様式・新集計）</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr"/>
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>⑤外部との比較可能性</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>全国・北海道・参加自治体と比較できる</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>区域内の経年比較ができる</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>当区域限り</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>点数</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>項目数</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>扱い</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>14〜15点</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>4項目</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>本文の成果指標とする。追加提供なしで毎年度算定でき、基準値も確定している。</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>11〜13点</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>3項目</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>本文の成果指標とする。ただしデータ源の一本化の決定（H05）、3年に1度であること（H04）、1回の抽出（H03）という条件が付く。</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>8〜10点</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>6項目</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>計画本文には掲げず、資料編に基準値のみを掲げる。定義変更の決定を要し、計画期間中は更新されない。</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>7点以下</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>3項目</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>指標から外す。追加提供がなければ算定できない。下表の代替により、施策の進み具合は別の形で確認する。</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>外した指標</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>測ろうとしていたこと</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>追加提供を要しない代替</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>出所</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>毎年度
+更新</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>留意点</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr"/>
+      <c r="J35" s="3" t="inlineStr"/>
+      <c r="K35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36" ht="76" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>H09 退院時支援調整実施率</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>医療と介護の連携の実効</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>交付金 支援目標Ⅲ（医療介護連携）の得点</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>厚生労働省の公表資料</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>得点は取組の有無の集合であり、個別の調整件数は表さない。第5章基本目標1のアウトプットとして「退院時カンファレンスの件数を把握する仕組みの整備（R9年度）」を置き、第11期に実測へ移す。</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="76" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>H10 認知症相談から支援接続までの適時率</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>認知症の早期対応</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>交付金 推進目標Ⅲ（認知症）の得点</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>厚生労働省の公表資料</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>同上。第5章基本目標2のアウトプットとして「認知症初期集中支援チームの対応件数」を置く。</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="5" t="inlineStr"/>
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="inlineStr"/>
+      <c r="L37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="76" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>H14 採用率と離職率の差</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>介護人材の定着</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>介護サービス情報公表システムの「介護職員の退職者数」「総従業者数」「経験年数5年以上の介護職員の割合」</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>介護サービス情報公表システム</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>受託者が収集した範囲では、退職者数は施設・居住系（特定施設・グループホーム等）に記載があり、訪問系には記載がない。施設・居住系に限った定着の指標となる。毎年度、公表画面からの転記作業が生じる。</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="inlineStr"/>
+      <c r="L38" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="39" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>注1）本表は、内部確認結果2項の「広域連合のみで追加して提供できる資料は現時点では多くない」というご回答を前提としたものである。追加提供が得られる場合は、H16（給付実績の減算の算定状況）とH14（各年9月30日現在の在籍者数）が優先度Bへ上がる。注2）本文の成果指標はA4項目＋B3項目の計7項目となる。第9期の代表KPIは4項目であったため、3項目の増にとどまる。注3）04シートで示した再整理案と1項目が入れ替わっている。04シートはH16を本文の成果指標としていたが、受領済みの給付費データに業務継続計画未策定減算の算定状況が含まれていないため、追加提供がない前提ではH16を優先度Cとし、代わりにH04（基準値19.1％が確定済み）を本文に残す。注4）優先度Dの3項目を外しても、医療介護連携・認知症・人材の定着は上表の代替により毎年度確認できる。いずれも公表資料であり、構成町に新たな事務を求めない。注5）本表は受託者の案である。ご協議をお願いする。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/第10期計画_内部確認結果への対応整理.xlsx
+++ b/output/第10期計画_内部確認結果への対応整理.xlsx
@@ -851,7 +851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1291,27 +1291,27 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>H16</t>
+          <t>H12</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>業務継続計画を策定している事業所の割合</t>
+          <t>区域内で提供できないサービスが必要と判断された利用者の割合</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>国民健康保険団体連合会の給付実績（業務継続計画未策定減算）</t>
+          <t>在宅生活改善調査 問3</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>3</v>
       </c>
       <c r="H12" s="4" t="n">
         <v>3</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>受領済みの給付費データに減算の算定状況が含まれるかを確認する。含まれていれば毎年度算定でき本文の成果指標とする。含まれない場合は国保連の給付実績の抽出を要するため、指標から外す。</t>
+          <t>資料編に基準値のみ（20.4％・98票中20票）。24時間対応サービスの整備の判断材料として重要だが3年に1度でしか更新されない。年次評価には、区域内に事業所がないサービスの数（毎年度、北海道の指定事業所一覧で確認できる）を用いる。</t>
         </is>
       </c>
     </row>
@@ -1339,24 +1339,24 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>H12</t>
+          <t>H07</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>区域内で提供できないサービスが必要と判断された利用者の割合</t>
+          <t>主に介護をしている者の割合</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善調査 問3</t>
+          <t>健康とくらしの調査 サブコア1【問17】4）</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>1</v>
@@ -1365,7 +1365,7 @@
         <v>3</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13" s="8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>資料編に基準値のみ（20.4％・98票中20票）。24時間対応サービスの整備の判断材料として重要だが3年に1度でしか更新されない。年次評価には、区域内に事業所がないサービスの数（毎年度、北海道の指定事業所一覧で確認できる）を用いる。</t>
+          <t>資料編に基準値のみ（3.4％・n=2,217）。指標の定義変更の決定を要する。</t>
         </is>
       </c>
     </row>
@@ -1387,45 +1387,45 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>H07</t>
+          <t>H16</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>主に介護をしている者の割合</t>
+          <t>業務継続計画を策定している事業所の割合</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>健康とくらしの調査 サブコア1【問17】4）</t>
+          <t>国民健康保険団体連合会の給付実績（業務継続計画未策定減算）</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>3</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>1</v>
+      </c>
+      <c r="J14" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>資料編に基準値のみ（3.4％・n=2,217）。指標の定義変更の決定を要する。</t>
+          <t>指標から外す。令和8年9月4日に受領済みの給付費データ12ファイルを点検した結果、加算・減算の内訳は収録されておらず（サービス種類コードまでの集約）、H16は算定できない。交付金の評価指標及び介護サービス情報公表システムにも業務継続計画に関する項目はない。代替は下表のとおり。</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>6項目</t>
+          <t>5項目</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2049,17 +2049,17 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>7点以下</t>
+          <t>7点以下、又は①が0点</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>3項目</t>
+          <t>4項目</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>指標から外す。追加提供がなければ算定できない。下表の代替により、施策の進み具合は別の形で確認する。</t>
+          <t>指標から外す。追加提供がなければ算定できない。①追加提供の要否が0点のものは、他の観点の点数にかかわらずDとする。算定できない指標は、水準の高低にかかわらず指標にならないためである。下表の代替により、施策の進み具合は別の形で確認する。</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr"/>
@@ -2189,22 +2189,22 @@
     <row r="38" ht="76" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>H14 採用率と離職率の差</t>
+          <t>H16 業務継続計画を策定している事業所の割合</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>介護人材の定着</t>
+          <t>災害・感染症時のサービス継続の備え</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>介護サービス情報公表システムの「介護職員の退職者数」「総従業者数」「経験年数5年以上の介護職員の割合」</t>
+          <t>指定・更新・運営指導の際に業務継続計画の策定を確認した地域密着型サービス事業所の数</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>介護サービス情報公表システム</t>
+          <t>広域連合が指定権者として保有する記録</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>受託者が収集した範囲では、退職者数は施設・居住系（特定施設・グループホーム等）に記載があり、訪問系には記載がない。施設・居住系に限った定着の指標となる。毎年度、公表画面からの転記作業が生じる。</t>
+          <t>区域内の地域密着型サービス事業所は17事業所（東川町4・美瑛町10・東神楽町3）である。特別養護老人ホーム・介護老人保健施設・訪問介護等の広域型は指定権者が北海道であるため含まれない。策定率ではなく確認件数のアウトプットとなる。</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
@@ -2224,16 +2224,54 @@
       <c r="K38" s="5" t="inlineStr"/>
       <c r="L38" s="5" t="inlineStr"/>
     </row>
-    <row r="40" ht="39" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>注1）本表は、内部確認結果2項の「広域連合のみで追加して提供できる資料は現時点では多くない」というご回答を前提としたものである。追加提供が得られる場合は、H16（給付実績の減算の算定状況）とH14（各年9月30日現在の在籍者数）が優先度Bへ上がる。注2）本文の成果指標はA4項目＋B3項目の計7項目となる。第9期の代表KPIは4項目であったため、3項目の増にとどまる。注3）04シートで示した再整理案と1項目が入れ替わっている。04シートはH16を本文の成果指標としていたが、受領済みの給付費データに業務継続計画未策定減算の算定状況が含まれていないため、追加提供がない前提ではH16を優先度Cとし、代わりにH04（基準値19.1％が確定済み）を本文に残す。注4）優先度Dの3項目を外しても、医療介護連携・認知症・人材の定着は上表の代替により毎年度確認できる。いずれも公表資料であり、構成町に新たな事務を求めない。注5）本表は受託者の案である。ご協議をお願いする。</t>
+    <row r="39" ht="76" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>H14 採用率と離職率の差</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>介護人材の定着</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>介護サービス情報公表システムの「介護職員の退職者数」「総従業者数」「経験年数5年以上の介護職員の割合」</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>介護サービス情報公表システム</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>受託者が収集した範囲では、退職者数は施設・居住系（特定施設・グループホーム等）に記載があり、訪問系には記載がない。施設・居住系に限った定着の指標となる。毎年度、公表画面からの転記作業が生じる。</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="inlineStr"/>
+      <c r="L39" s="5" t="inlineStr"/>
+    </row>
+    <row r="41" ht="39" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>注1）本表は、内部確認結果2項の「広域連合のみで追加して提供できる資料は現時点では多くない」というご回答を前提としたものである。追加提供が得られる場合は、H16（国保連の給付実績の明細情報）とH14（各年9月30日現在の在籍者数）が優先度Bへ上がる。注2）本文の成果指標はA4項目＋B3項目の計7項目となる。第9期の代表KPIは4項目であったため、3項目の増にとどまる。注3）04シートで示した再整理案と1項目が入れ替わっている。04シートはH16を本文の成果指標としていたが、令和8年9月4日に受領済みの給付費データ12ファイルを点検した結果、加算・減算の内訳が収録されておらず算定できないことが確定した（給付実績データの受領点検 05シート）。このためH16を優先度Dとし、代わりにH04（基準値19.1％が確定済み）を本文に残す。注4）優先度Dの4項目を外しても、医療介護連携・認知症・人材の定着・業務継続計画は上表の代替により毎年度確認できる。H09・H10・H14の代替は公表資料であり、H16の代替は広域連合が指定権者として保有する記録である。いずれも構成町に新たな事務を求めない。注5）本表は受託者の案である。ご協議をお願いする。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="A41:L41"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
@@ -4173,22 +4211,22 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>不要</t>
+          <t>必要（明細情報の抽出）</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>直結</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>本文の成果指標として残す</t>
+          <t>間接</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>指標から外し、施策のアウトプットに置き換える</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>令和6年度の報酬改定で同減算が新設されており、給付実績から毎年度算定できる。事業所への調査を要しない。給付実績の提供を継続していただく必要がある。</t>
+          <t>令和6年度の報酬改定で同減算が新設されているが、受領済みの給付費データ12ファイルには加算・減算の内訳が収録されていないことを令和8年9月4日に確認した（09シート・給付実績データの受領点検 05シート）。国保連の給付実績（明細情報）の抽出が得られれば毎年度算定できる。</t>
         </is>
       </c>
     </row>
@@ -4222,12 +4260,12 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>H01・H02・H03・H05・H13・H15・H16</t>
+          <t>H01・H02・H03・H05・H13・H15</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>毎年度、既存の統計・システム・給付実績から算定でき、構成町に新たな事務を求めないもの。7項目。</t>
+          <t>毎年度、既存の統計・システムから算定でき、構成町に新たな事務を求めないもの。6項目。</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr"/>
@@ -4288,12 +4326,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>H09・H10</t>
+          <t>H09・H10・H16</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>構成町に新たな記録様式の整備を求めるもの。2項目。</t>
+          <t>構成町に新たな記録様式の整備を求めるもの（H09・H10）、又はデータ源そのものが得られないもの（H16）。3項目。</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr"/>
@@ -4327,7 +4365,7 @@
     <row r="29" ht="52" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>注1）本文の成果指標は12項目から7項目になり、補完指標4項目は廃止する。計画本文に掲げる指標は7項目、資料1に基準値のみ掲げる指標が3項目である。注2）「取得頻度」が3年に1度の指標は、第10期の計画期間（令和9〜11年度）中に更新されない。次の調査は第11期計画の策定時（令和11年度）である。注3）保険料算定・介護保険運営に直接関係する事項（高齢者人口、要介護認定率、サービス見込量、給付費、保険料）は、代表KPIとは別に第2章・第6章で毎年度の実績と対比する。H01・H02・H03・H15がこれに対応する。注4）「KPI」という表現には、資料1の冒頭に「計画の達成状況を測るための指標」という用語説明を加え、第9期の代表KPI4項目との対応表を併せて示す。注5）本シートは受託者の案である。ご協議をお願いする。</t>
+          <t>注1）本文の成果指標は12項目から6項目になり、補完指標4項目は廃止する。09シートの優先順位ではH04を本文に残すため7項目となる。資料1に基準値のみ掲げる指標が3項目である。注2）「取得頻度」が3年に1度の指標は、第10期の計画期間（令和9〜11年度）中に更新されない。次の調査は第11期計画の策定時（令和11年度）である。注3）保険料算定・介護保険運営に直接関係する事項（高齢者人口、要介護認定率、サービス見込量、給付費、保険料）は、代表KPIとは別に第2章・第6章で毎年度の実績と対比する。H01・H02・H03・H15がこれに対応する。注4）「KPI」という表現には、資料1の冒頭に「計画の達成状況を測るための指標」という用語説明を加え、第9期の代表KPI4項目との対応表を併せて示す。注5）本シートは受託者の案である。ご協議をお願いする。</t>
         </is>
       </c>
     </row>
